--- a/files/week-09-smartsheet-resource-workout.xlsx
+++ b/files/week-09-smartsheet-resource-workout.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Smartsheet Import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,10 +32,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -87,12 +84,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,17 +455,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -495,22 +492,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Allocation %</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Coordinators</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinators needed</t>
         </is>
       </c>
     </row>
@@ -531,20 +533,21 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="n">
+        <v>46328</v>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Kim</t>
         </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>2000</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="I2" s="5" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -567,20 +570,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Kim, Lee</t>
         </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>30000</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="I3" s="5" t="n">
+        <v>30000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -603,20 +605,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Ortiz</t>
         </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>6000</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="I4" s="5" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -639,20 +640,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Kim</t>
         </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>8000</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="I5" s="5" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -675,20 +675,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Lee, Ortiz</t>
         </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>12000</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="I6" s="5" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -711,20 +710,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Kim, Lee</t>
         </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2500</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="I7" s="5" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -747,20 +745,19 @@
           <t>4, 5</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Kim</t>
         </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>3000</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="I8" s="5" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -783,20 +780,19 @@
           <t>6, 7</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Kim, Lee</t>
         </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>4000</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="I9" s="5" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -819,411 +815,18 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Lee, Ortiz</t>
         </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2500</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Import this tab. Predecessors are Smartsheet row numbers (A = row 1). Assigned To holds the early-start assignment of three coordinators; Allocation % is 100 per person.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Column or field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Smartsheet formula</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Cost per day</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C2" s="6">
-        <f>Cost@row / NETWORKDAYS([Start Date]@row, [End Date]@row)</f>
-        <v/>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Direct cost spread evenly over the activity's workdays</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Workday start</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C3" s="6">
-        <f>NETWORKDAYS([Start Date]$1, [Start Date]@row) - 1</f>
-        <v/>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>0 = project start; matches the notes' day numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Workday finish</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C4" s="6">
-        <f>NETWORKDAYS([Start Date]$1, [End Date]@row)</f>
-        <v/>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Finish day as the notes count it</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Wk 1 PV</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C5" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 11, 2), [Start Date]@row, DATE(2026, 11, 2)), IF([End Date]@row &lt; DATE(2026, 11, 6), [End Date]@row, DATE(2026, 11, 6)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 1: Mon 2 Nov to Fri 6 Nov</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Wk 2 PV</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C6" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 11, 9), [Start Date]@row, DATE(2026, 11, 9)), IF([End Date]@row &lt; DATE(2026, 11, 13), [End Date]@row, DATE(2026, 11, 13)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 2: Mon 9 Nov to Fri 13 Nov</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Wk 3 PV</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C7" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 11, 16), [Start Date]@row, DATE(2026, 11, 16)), IF([End Date]@row &lt; DATE(2026, 11, 20), [End Date]@row, DATE(2026, 11, 20)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 3: Mon 16 Nov to Fri 20 Nov</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Wk 4 PV</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C8" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 11, 23), [Start Date]@row, DATE(2026, 11, 23)), IF([End Date]@row &lt; DATE(2026, 11, 27), [End Date]@row, DATE(2026, 11, 27)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 4: Mon 23 Nov to Fri 27 Nov</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Wk 5 PV</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C9" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 11, 30), [Start Date]@row, DATE(2026, 11, 30)), IF([End Date]@row &lt; DATE(2026, 12, 4), [End Date]@row, DATE(2026, 12, 4)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 5: Mon 30 Nov to Fri 4 Dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Wk 6 PV</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C10" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 12, 7), [Start Date]@row, DATE(2026, 12, 7)), IF([End Date]@row &lt; DATE(2026, 12, 11), [End Date]@row, DATE(2026, 12, 11)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 6: Mon 7 Dec to Fri 11 Dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Wk 7 PV</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C11" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 12, 14), [Start Date]@row, DATE(2026, 12, 14)), IF([End Date]@row &lt; DATE(2026, 12, 18), [End Date]@row, DATE(2026, 12, 18)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 7: Mon 14 Dec to Fri 18 Dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Wk 8 PV</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C12" s="6">
-        <f>MAX(0, NETWORKDAYS(IF([Start Date]@row &gt; DATE(2026, 12, 21), [Start Date]@row, DATE(2026, 12, 21)), IF([End Date]@row &lt; DATE(2026, 12, 25), [End Date]@row, DATE(2026, 12, 25)))) * [Cost per day]@row</f>
-        <v/>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Planned value in week 8: Mon 21 Dec to Fri 25 Dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Project finish</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Sheet Summary</t>
-        </is>
-      </c>
-      <c r="C13" s="6">
-        <f>MAX([End Date]:[End Date])</f>
-        <v/>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Date type</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Workdays</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Sheet Summary</t>
-        </is>
-      </c>
-      <c r="C14" s="6">
-        <f>MAX([Workday finish]:[Workday finish])</f>
-        <v/>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>25 on the early-start schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Wk n total</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Sheet Summary</t>
-        </is>
-      </c>
-      <c r="C15" s="6">
-        <f>SUM([Wk 1 PV]:[Wk 1 PV])  (one field per week)</f>
-        <v/>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Weekly planned value</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Cumulative to wk n</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Sheet Summary</t>
-        </is>
-      </c>
-      <c r="C16" s="6">
-        <f>[Wk 1 total]# + [Wk 2 total]#  (extend per week)</f>
-        <v/>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>The baseline curve</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Total cost</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Sheet Summary</t>
-        </is>
-      </c>
-      <c r="C17" s="6">
-        <f>SUM(Cost:Cost)</f>
-        <v/>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Must read $70,000 under every schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Smartsheet imports values, not formulas. Type each formula once in row 1, then right-click → Convert to Column Formula. Summary fields are typed in the Sheet Summary panel.</t>
-        </is>
+      <c r="I10" s="5" t="n">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
